--- a/AAII_Financials/Quarterly/ETR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>ETR</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3523600</v>
+      </c>
+      <c r="E8" s="3">
         <v>3187600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2958900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3812000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3328800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2846900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2742300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3389100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2953600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2794600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2724800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3595500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2846000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2981100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3272500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4218600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3395200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2877900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2722500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3353500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2822100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2844800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2370100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2903600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2412800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2427200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2462300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3140600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2666200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2609600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2512500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3104300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2668800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2723900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2623800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3243600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2618600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2588500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2648500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3124700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1866400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1672600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1717600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1888900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1766500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1396000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1487800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1620200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1463300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1570100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1719900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1807700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1484900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1805400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2178600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2614700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2037200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1658400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1743300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1793000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1703300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1631400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1472700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1482300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1334100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1366300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1571400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1771000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1706000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1651300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1822300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2060600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1758300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1665700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1744600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1839400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1645700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1664800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1828300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1725900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1657200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1515100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1241400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1923100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1562400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1450900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1254500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1768900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1490300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1224600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1004900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1787800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1361100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1175600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1093900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1603900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1358000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1219500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>979200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1560500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1118800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1213400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>897400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1421300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1078700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1060900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>890900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1369600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>960200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>958300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>690200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1043700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>910500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1058200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>879200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1404200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>972900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>923700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>820200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1398800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>18100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-7700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-21600</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>325300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>131800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>45000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>138400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-164100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-81600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>342100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>198100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>16400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>74000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>235200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>155200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>68900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>72900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>133100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>16200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>193600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>195500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>2802500</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>18800</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>548200</v>
+      </c>
+      <c r="E15" s="3">
         <v>540100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>516800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>525400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>522600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>512900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>509700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>498500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>505400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>499700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>482300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>439900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>468900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>453900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>424000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>453300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>444800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>439000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>426500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>421700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>421500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>414500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>408000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>401600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>403800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>399700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>380000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>379200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>363500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>357300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>347300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>324600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>350500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>347100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>337600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>354700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>350300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>347300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>336800</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>340400</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2661800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2593200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2397200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2666300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2479000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2134400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2082400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2248400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2318100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2408200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2451900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2404200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2082600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2511700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2823600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3263900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3314100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2311900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2380900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2525700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2653900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2336800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2218000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2125600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1973500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2027400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2213800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2620600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2327400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2326300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2741400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2833300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2577200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2388200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2386800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2484600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2449700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2393000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5247500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2352600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>861800</v>
+      </c>
+      <c r="E18" s="3">
         <v>594400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>561800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1145700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>849800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>712500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>659900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1140700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>635500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>386400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>272900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1191300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>763500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>469300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>448900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>954700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>81100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>566000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>341600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>827800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>168200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>508000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>152100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>778000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>439300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>399800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>248500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>520000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>338800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>283300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-228900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>271000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>91600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>335700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>237000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>759000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>168900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>195500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-2599000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>772100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-86300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-32600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-16200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-64900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-19400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>35200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>30100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>47500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>13500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-109500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-44800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-49900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>101300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>75500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>97000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>145700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>93800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>219600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-157500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>85800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>65300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>87500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>201700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-170300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>165900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>54300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>13800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>87900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>51400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>70200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>60300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>31900</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>46200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1425900</v>
+      </c>
+      <c r="E21" s="3">
         <v>1220900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1087900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1703700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1388600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1290400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1188900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1603900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1146700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>856000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>707700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1643900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1218900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1032700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>926700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1521300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>583500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1129300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>989500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1449400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>763300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1185500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>860700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1435600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1221500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>810800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>881900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1151200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>964900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1015200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>124000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>926600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>648300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>874700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>842000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1329200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>750400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>787200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1354400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>433100</v>
+      </c>
+      <c r="E22" s="3">
         <v>399900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>374500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>347000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>343100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>348400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>316100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>308500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>301300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>277700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>264600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>264900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>261300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>255300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>236400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>227500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>226900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>221500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>211900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>209500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>213400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>199900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>194100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>196700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>204700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>190100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>187900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>186600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>184300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>183500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>180000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>180100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>177600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>169700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>170500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>166900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>162900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>162000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>164500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>167200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>614300</v>
+      </c>
+      <c r="E23" s="3">
         <v>472700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>290000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>899100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>606300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>460800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>397400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>860400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>82600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>96300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>893800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>526000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>232000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>167700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>740000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-195600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>346100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>231000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>693900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-19800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>405100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>103700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>675100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>454200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>52100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>146400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>398700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>242000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>301400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-579200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>256800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-31700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>179900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>154400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>643400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>76300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>93800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-2731700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>651100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E24" s="3">
         <v>87800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>54200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>205300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>138400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>110900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>215500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-973400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>227000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>134800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>70100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>184100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-359600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>66500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-14400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>158300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-18400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>65900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-288900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>149400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>89100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-243300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>29200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>42800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-515300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-283000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-280600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>42100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>69700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>241800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-337100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>7800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-966100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>257900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E26" s="3">
         <v>384900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>235800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>693800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>467900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>360800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>286400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>644900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>48900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>75300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>987600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>666800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>391200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>310900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>97700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>555900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>164000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>279600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>245400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>535600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>339100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>392500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>525700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>365100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>123300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>389600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>369500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>240500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>258600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-63900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>539800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>248900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>137800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>84700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>401600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>413400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>86100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-1765500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>393200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E27" s="3">
         <v>384900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>235800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>693800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>467900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>360800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>286400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>644900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>48900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>75300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>987600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>666800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>391200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>310900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>106500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>560600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>159700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>276400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>258900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>531000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>334600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>388000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>521100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>360500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>118700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>385000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>365200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>236400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>254500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-67500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>536400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>245400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>134400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>81300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>398200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>409900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>82600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-1769100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>388200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3242,23 +3303,23 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>1600</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-560400</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E32" s="3">
         <v>86300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>32600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>16200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>64900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>19400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-35200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-30100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-47500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-13500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>109500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>44800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>49900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-101300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-75500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-145700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-93800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-219600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>157500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-85800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-65300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-87500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-201700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>170300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-165900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-54300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-13800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-87900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-51400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-70200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-60300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-31900</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-46200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E33" s="3">
         <v>384900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>235800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>693800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>467900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>360800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>286400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>644900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>48900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>75300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>987600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>666800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>391200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>310900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>106500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>560600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>159700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>276400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>258900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>531000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>334600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>388000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>521100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>360500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>118700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>385000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>365200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>236400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>254500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-65900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>536400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>245400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>132800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-479100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>398200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>409900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>82600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-1769100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>388200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E35" s="3">
         <v>384900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>235800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>693800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>467900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>360800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>286400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>644900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>48900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>75300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>987600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>666800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>391200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>310900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>106500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>560600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>159700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>276400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>258900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>531000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>334600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>388000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>521100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>360500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>118700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>385000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>365200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>236400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>254500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-65900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>536400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>245400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>132800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-479100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>398200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>409900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>82600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-1769100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>388200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3854000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3571100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1928900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1517000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1175600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1513400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>859700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1411800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1355200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1294900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>132500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1519800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1194300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1970500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>224200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1003500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>579900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>76100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>44900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>44200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>157300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>67600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>128900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>43900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>55500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>283500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>34200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>70400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>61200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>118400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>56700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>64800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>57900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>56600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>87300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>67200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>60900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>129600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>101900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4353,7 +4443,7 @@
         <v>1000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -4395,609 +4485,624 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>625400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>397600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>955800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>529600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1675100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1630200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1195800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>880000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1180300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>391500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>885400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>574700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>865100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>424300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>923200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>757600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1147700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>724600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>459000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>867300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1050200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1089300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1205600</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1708500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1432200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1470200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1780400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1665400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1338900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1390400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1666600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1581000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1285500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1393500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1712700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1430000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1240700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>999400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1168500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1017500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>809000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>950100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1045200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>926300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>923200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>850900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>894000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>712800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>706100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>808000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>857300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>776500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>740400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>718900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>940300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>798300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>765200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>829100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>893200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>705000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>633900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>801500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>940900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1922200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1883400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1842400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1807900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1798600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1703700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1797500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1779200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1750900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1682600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1611800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1544300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1498900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1410600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1330900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1264600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1232800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1206300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1196100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1158200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1146300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1118800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1135100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1065000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1036300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>998700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>970500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>935500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>917700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>893400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>870100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>880700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>926700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>940600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>905900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>878600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>869100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>854400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>878100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1107200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>381200</v>
+      </c>
+      <c r="E45" s="3">
         <v>486500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>167600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>117000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>270400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>254700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>137500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>144100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>261900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>278600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>331100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>347000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>387600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>447100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1540500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2073200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1965300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1122100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1034800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1029200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1035200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1003900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>814800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>864100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>862400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>805300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>841800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>913000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>953300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>790500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>888000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>885600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>996700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>744400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>769100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1153100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1090800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>798100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>785800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>984500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8204200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7810100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5806900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5558800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5189500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5112400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4396200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5217800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5147100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4757800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3660900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5329700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4692600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5266200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4095000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5509800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4795400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3839000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3623600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4232700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3794700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4788600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4559900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4062800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3547000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3974000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3046000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3661700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3283500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3407800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2958100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3694500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3534500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3655700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3285300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3471200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3599300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3397500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3684300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4340000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E47" s="3">
         <v>123200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>124400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>85700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>84400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>82900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>82300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>72100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>71900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>70300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>69500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>65600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>99900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>101500</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5047,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="AH47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3">
         <v>200</v>
@@ -5071,132 +5176,138 @@
         <v>200</v>
       </c>
       <c r="AP47" s="3">
+        <v>200</v>
+      </c>
+      <c r="AQ47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>57603400</v>
+      </c>
+      <c r="E48" s="3">
         <v>55368600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53336200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51754500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50474200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>49140400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>47846700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46863700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>45585200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44919600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44252900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43715000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43275200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42522700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42843500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>42079600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41572300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>41551200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>42601700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41541700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>39784800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>39377900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>39196100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>38342200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>36645000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>36116400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>35515600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>34447400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>33869100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>32962400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>32278800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>31395500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>30806700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>30391700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>29925300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>29213400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>28814600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>28417000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>28155000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>29552100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5213,13 +5324,13 @@
         <v>367600</v>
       </c>
       <c r="H49" s="3">
+        <v>367600</v>
+      </c>
+      <c r="I49" s="3">
         <v>367700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>367600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>374100</v>
       </c>
       <c r="K49" s="3">
         <v>374100</v>
@@ -5231,7 +5342,7 @@
         <v>374100</v>
       </c>
       <c r="N49" s="3">
-        <v>377200</v>
+        <v>374100</v>
       </c>
       <c r="O49" s="3">
         <v>377200</v>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>377200</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>377200</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7617100</v>
+      </c>
+      <c r="E52" s="3">
         <v>7048900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7062000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6898700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6987600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6618100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6650400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6258900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5990600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5890000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5488100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5151400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5316200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5118400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11279500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11008800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11082700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14066100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12851700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12692000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11992600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14124100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14106000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13288100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12796100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>12087500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12785200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12020000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13036000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12858000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12661000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>13003700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>12904200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>12856700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>13119100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>13336500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>13215700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>13126300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>13687700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>13468100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>79002600</v>
+      </c>
+      <c r="E54" s="3">
         <v>75804100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71890700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69848400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68383100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66620400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64790000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>64462000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62766300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>61629900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>59703400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>60552100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>59717200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59203300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58595200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58975300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57827600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>59833500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59454200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58843500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>55949300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58667600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>58239200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>56070300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>53365300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>52555000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>51723900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>50506300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>50565700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>49605400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>48275100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>48471200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>47622600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>47281500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>46707100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>46398400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>46007000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>45318200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>45904400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>47738200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2716200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2748800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2565500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2184700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2133800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1809900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1929200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1523300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1314700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1187500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1566700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1336100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1523700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1385900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1777600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1744200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1935300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1741100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2610100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3452200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1348700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1697200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2739400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2872400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1509400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1502400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1499900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1328600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1412600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1406300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1496100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1392100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1459400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1260700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1452200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1105000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1165700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1149500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1285600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1063100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3079700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2907500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3120900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3390000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2290700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2660100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2389500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2439500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2449400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4090600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3314700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2875200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2957400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3124700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3136700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2970700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2306900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2382100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2240500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1776700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1151600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1656600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2791500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2448200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3151200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3171800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2753200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2449300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1796600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2103900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2594000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2683200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3002500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2066600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2339800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2223900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1954300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1659800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>782300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1186300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2810200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2108600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1787700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1862800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1744500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1396000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1467900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1568300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1428800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1305300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1241400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1322100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1109000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1001200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1455200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1440000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1299400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1240000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1340100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1416000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1304200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1158100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1529600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1554900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1455300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1343700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1367500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1325100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1313400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1350800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1353500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1675300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1770200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1905400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1244200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1131900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1120600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1069700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1132200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1202300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8998600</v>
+      </c>
+      <c r="E60" s="3">
         <v>8160000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7823000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7791200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6512900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6200300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6111000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5859200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5487200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6884500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6396500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5848700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5881300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5825300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6369400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6154900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5541600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5363200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6190700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6644900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3804500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4511900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7060500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6875500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6115900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6017900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5620500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5103000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4522600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4861100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5443500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5750600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6232100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5232700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5036200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4460900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4240500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3879000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3200100</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>3451700</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31547700</v>
+      </c>
+      <c r="E61" s="3">
         <v>31150900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28208000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27058100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28114700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28264900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26924300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26563400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26301100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24309400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23227700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24659300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24321700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24464300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23623500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24635900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24543900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>26176400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24841600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23846700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24212000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>24075500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>21205800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>19612700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>18278400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>18228500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17132000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16991300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>17257700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>17221000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15538700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15801700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14878900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>15613300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>14337300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>14000300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>14330900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>13950800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>14492200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>13886700</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11682600</v>
+      </c>
+      <c r="E62" s="3">
         <v>11165400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11117000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11257500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11002100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10962300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10799100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11470400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11035600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10629600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9724300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9820400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9748300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9413100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15317900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15770800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15704100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16297700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16497100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16845000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16790400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18808700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18792400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18555800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18290600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>17830200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18493300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>18122500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>18768500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>18333600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>18229100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>18308400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>18291400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>18262900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>19143400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>19043800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>18861500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>19228000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>19927100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>20097500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60462500</v>
+      </c>
+      <c r="E66" s="3">
         <v>58146600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54657200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52872600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>51854800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51118600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49385600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>49100900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47865200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46836100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>44740900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46513700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46130300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45816900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45310900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>46561600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>45789600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>47837300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>47529400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47336600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>44806900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47396000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47058700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45044000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>42684900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>42076700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>41245800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>40216800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>40548800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>40415600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>39211400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>39860700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>39402400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>39108800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>38516800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>37505000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>37433000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>37057800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>37619400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>37435900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7568,22 +7736,22 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>317300</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>317300</v>
       </c>
       <c r="S70" s="3">
+        <v>317300</v>
+      </c>
+      <c r="T70" s="3">
         <v>326900</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>286100</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>287500</v>
-      </c>
-      <c r="V70" s="3">
-        <v>254400</v>
       </c>
       <c r="W70" s="3">
         <v>254400</v>
@@ -7610,7 +7778,7 @@
         <v>254400</v>
       </c>
       <c r="AE70" s="3">
-        <v>219400</v>
+        <v>254400</v>
       </c>
       <c r="AF70" s="3">
         <v>219400</v>
@@ -7619,7 +7787,7 @@
         <v>219400</v>
       </c>
       <c r="AH70" s="3">
-        <v>197800</v>
+        <v>219400</v>
       </c>
       <c r="AI70" s="3">
         <v>197800</v>
@@ -7631,7 +7799,7 @@
         <v>197800</v>
       </c>
       <c r="AL70" s="3">
-        <v>203200</v>
+        <v>197800</v>
       </c>
       <c r="AM70" s="3">
         <v>203200</v>
@@ -7643,10 +7811,13 @@
         <v>203200</v>
       </c>
       <c r="AP70" s="3">
+        <v>203200</v>
+      </c>
+      <c r="AQ70" s="3">
         <v>233200</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12980100</v>
+      </c>
+      <c r="E72" s="3">
         <v>12790500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12698400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12752200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12326300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12116800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12014300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11985600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11582300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11774700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11940400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11192300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10751800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10586800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10502000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10621300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10266200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10311900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10240600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10184600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9844500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10041200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9897200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9699400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9364500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9190100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9257600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9057700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8873500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8809900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8721200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8953600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8578300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8493800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7977700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8617900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8375900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8122100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8195600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10123100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18229100</v>
+      </c>
+      <c r="E76" s="3">
         <v>17346700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16923100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16661700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16213000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15185300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15083900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15032800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14567700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14458300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14622600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13691500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13237100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13058200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12967000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12096400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11711100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11710100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11637300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11252500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10887900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11017200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10926100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10771800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10426000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10224000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10223700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10035100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9797500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8970400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8844300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8412700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8022500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7974900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7992500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8690200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8370900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>8057200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>8081800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>10069100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E81" s="3">
         <v>384900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>235800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>693800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>467900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>360800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>286400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>644900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>48900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>75300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>987600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>666800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>391200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>310900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>106500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>560600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>159700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>276400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>258900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>531000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>334600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>388000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>521100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>360500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>118700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>385000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>365200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>236400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>254500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-65900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>536400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>245400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>132800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-479100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>398200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>409900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>82600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-1769100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>388200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>576100</v>
+      </c>
+      <c r="E83" s="3">
         <v>566600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>565100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>559400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>551900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>547000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>523200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>499400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>512500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>502700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>472700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>504500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>489400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>499700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>522600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>553800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>552200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>561700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>546600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>546000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>569700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>580600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>562800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>563700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>562600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>568600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>547600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>565900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>538600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>530200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>523200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>489700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>502400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>525200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>517000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>518900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>511300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>531400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>574400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>536100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1892800</v>
+      </c>
+      <c r="E89" s="3">
         <v>829000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1218100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2134800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1261600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>536200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1379700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1562400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1025400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>521100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1063300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1405000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>866400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>959500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>776000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>993500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>278000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>538000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>289700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1264400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>796100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-49600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>319700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>921900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>789200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>659100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>698700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1064900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>551900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>501200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>525700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>779600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>522500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>557400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>910700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>893100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>290300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>529400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>746300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1000300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2773100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2355700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2161900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1882900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2009900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1706000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1909700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1524600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1162000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1240300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1115200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1104400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1185300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1243300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1304100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1144300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1362800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1584900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2332300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1096000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>11400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-47900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-191000</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-73200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>144200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-80500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-40700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>209300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-72100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-932100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-931200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-746600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2671100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2421900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1898100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1470500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2030500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1710400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1847400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1535100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1178600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1287900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1049900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1133600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1161800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1283600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1340900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1672800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1551200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2317300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1035800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1313000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1513300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1516400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1057700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1152700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1045500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1485300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-999900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-951000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1070800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-955300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-974400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1013300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1057500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-958400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-811800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-867600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-716300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E96" s="3">
         <v>292900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>289500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>267900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>258500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>258200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>257700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>241700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>241300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>241000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>239500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>226300</v>
-      </c>
-      <c r="O96" s="3">
-        <v>226200</v>
       </c>
       <c r="P96" s="3">
         <v>226200</v>
       </c>
       <c r="Q96" s="3">
+        <v>226200</v>
+      </c>
+      <c r="R96" s="3">
         <v>-225700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-205500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-205400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-205100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-203000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-190900</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-190600</v>
       </c>
       <c r="X96" s="3">
         <v>-190600</v>
       </c>
       <c r="Y96" s="3">
+        <v>-190600</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-190200</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-186200</v>
       </c>
       <c r="AA96" s="3">
         <v>-186200</v>
       </c>
       <c r="AB96" s="3">
+        <v>-186200</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-185800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-185200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-181000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-172900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-172600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-164800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-161000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-160900</v>
       </c>
       <c r="AJ96" s="3">
         <v>-160900</v>
       </c>
       <c r="AK96" s="3">
+        <v>-160900</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-160500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-156200</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-156100</v>
       </c>
       <c r="AN96" s="3">
         <v>-156100</v>
       </c>
       <c r="AO96" s="3">
+        <v>-156100</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-155800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-152200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1061300</v>
+      </c>
+      <c r="E100" s="3">
         <v>3235100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1092000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-322900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>431100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1827900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-84400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>29400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>213600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1929100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>54000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-480800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2070400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-214400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>575100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1273100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1272300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1470100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>84500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-538900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1546400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1716200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>440000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-164900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1424500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>256500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>255000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>174600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>952300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>72800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>466400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>39900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>841400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>337600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-223800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>519500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>177600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1642100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>411900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>341300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-337800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>653700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-552100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>56600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>60300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1162300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1387200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>325400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-776200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1746300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-779300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>423600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-121700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>259000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-557500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>313200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>519400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>304200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-528400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1038100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-530100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>319900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-347600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>502500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-507000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>175200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-392800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>424300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>235000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-388200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-148600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-104800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-119600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>311300</v>
       </c>
     </row>
